--- a/toolkit/function-cost-matrix.xlsx
+++ b/toolkit/function-cost-matrix.xlsx
@@ -601,9 +601,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -669,7 +666,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Component € (row total)</t>
+          <t>Component £ (row total)</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1196,7 @@
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>How to use: list components down column A, name your functions across F1–F6 (rename the headers to your verb–noun functions), and split each component's € cost across the functions it serves. Row totals must equal the component cost; the bottom row totals each function's cost. Need more components? Insert rows above 'Function cost total' (formulas copy down). Need more functions? Insert columns before 'Other'.</t>
+          <t>How to use: list components down column A, name your functions across F1–F6 (rename the headers to your verb–noun functions), and split each component's £ cost across the functions it serves. Row totals must equal the component cost; the bottom row totals each function's cost. Need more components? Insert rows above 'Function cost total' (formulas copy down). Need more functions? Insert columns before 'Other'.</t>
         </is>
       </c>
     </row>
@@ -1260,9 +1257,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -1276,12 +1270,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Cost €</t>
+          <t>Cost £</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Worth € (floor)</t>
+          <t>Worth £ (floor)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1317,7 +1311,7 @@
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>IF(D7=0,"",IF(C7/D7&lt;1.2,"Healthy",IF(C7/D7&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D7=0,"",IF(C7/D7&lt;=1.2,"Healthy",IF(C7/D7&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1337,7 @@
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IF(D8=0,"",IF(C8/D8&lt;1.2,"Healthy",IF(C8/D8&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D8=0,"",IF(C8/D8&lt;=1.2,"Healthy",IF(C8/D8&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1357,7 +1351,7 @@
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IF(D9=0,"",IF(C9/D9&lt;1.2,"Healthy",IF(C9/D9&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D9=0,"",IF(C9/D9&lt;=1.2,"Healthy",IF(C9/D9&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1365,7 @@
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IF(D10=0,"",IF(C10/D10&lt;1.2,"Healthy",IF(C10/D10&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D10=0,"",IF(C10/D10&lt;=1.2,"Healthy",IF(C10/D10&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1385,7 +1379,7 @@
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IF(D11=0,"",IF(C11/D11&lt;1.2,"Healthy",IF(C11/D11&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D11=0,"",IF(C11/D11&lt;=1.2,"Healthy",IF(C11/D11&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1399,7 +1393,7 @@
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IF(D12=0,"",IF(C12/D12&lt;1.2,"Healthy",IF(C12/D12&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D12=0,"",IF(C12/D12&lt;=1.2,"Healthy",IF(C12/D12&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1413,7 +1407,7 @@
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IF(D13=0,"",IF(C13/D13&lt;1.2,"Healthy",IF(C13/D13&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D13=0,"",IF(C13/D13&lt;=1.2,"Healthy",IF(C13/D13&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1421,7 @@
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>IF(D14=0,"",IF(C14/D14&lt;1.2,"Healthy",IF(C14/D14&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D14=0,"",IF(C14/D14&lt;=1.2,"Healthy",IF(C14/D14&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1441,7 +1435,7 @@
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>IF(D15=0,"",IF(C15/D15&lt;1.2,"Healthy",IF(C15/D15&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D15=0,"",IF(C15/D15&lt;=1.2,"Healthy",IF(C15/D15&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1449,7 @@
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>IF(D16=0,"",IF(C16/D16&lt;1.2,"Healthy",IF(C16/D16&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D16=0,"",IF(C16/D16&lt;=1.2,"Healthy",IF(C16/D16&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1469,7 +1463,7 @@
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>IF(D17=0,"",IF(C17/D17&lt;1.2,"Healthy",IF(C17/D17&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D17=0,"",IF(C17/D17&lt;=1.2,"Healthy",IF(C17/D17&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1483,7 +1477,7 @@
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>IF(D18=0,"",IF(C18/D18&lt;1.2,"Healthy",IF(C18/D18&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D18=0,"",IF(C18/D18&lt;=1.2,"Healthy",IF(C18/D18&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1497,7 +1491,7 @@
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>IF(D19=0,"",IF(C19/D19&lt;1.2,"Healthy",IF(C19/D19&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D19=0,"",IF(C19/D19&lt;=1.2,"Healthy",IF(C19/D19&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1511,7 +1505,7 @@
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>IF(D20=0,"",IF(C20/D20&lt;1.2,"Healthy",IF(C20/D20&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D20=0,"",IF(C20/D20&lt;=1.2,"Healthy",IF(C20/D20&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1519,7 @@
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>IF(D21=0,"",IF(C21/D21&lt;1.2,"Healthy",IF(C21/D21&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D21=0,"",IF(C21/D21&lt;=1.2,"Healthy",IF(C21/D21&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1539,7 +1533,7 @@
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>IF(D22=0,"",IF(C22/D22&lt;1.2,"Healthy",IF(C22/D22&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D22=0,"",IF(C22/D22&lt;=1.2,"Healthy",IF(C22/D22&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1553,7 +1547,7 @@
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>IF(D23=0,"",IF(C23/D23&lt;1.2,"Healthy",IF(C23/D23&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D23=0,"",IF(C23/D23&lt;=1.2,"Healthy",IF(C23/D23&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1567,7 +1561,7 @@
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>IF(D24=0,"",IF(C24/D24&lt;1.2,"Healthy",IF(C24/D24&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D24=0,"",IF(C24/D24&lt;=1.2,"Healthy",IF(C24/D24&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1581,7 +1575,7 @@
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>IF(D25=0,"",IF(C25/D25&lt;1.2,"Healthy",IF(C25/D25&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D25=0,"",IF(C25/D25&lt;=1.2,"Healthy",IF(C25/D25&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1595,7 +1589,7 @@
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>IF(D26=0,"",IF(C26/D26&lt;1.2,"Healthy",IF(C26/D26&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D26=0,"",IF(C26/D26&lt;=1.2,"Healthy",IF(C26/D26&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1609,7 +1603,7 @@
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>IF(D27=0,"",IF(C27/D27&lt;1.2,"Healthy",IF(C27/D27&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D27=0,"",IF(C27/D27&lt;=1.2,"Healthy",IF(C27/D27&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1617,7 @@
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>IF(D28=0,"",IF(C28/D28&lt;1.2,"Healthy",IF(C28/D28&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D28=0,"",IF(C28/D28&lt;=1.2,"Healthy",IF(C28/D28&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1631,7 @@
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>IF(D29=0,"",IF(C29/D29&lt;1.2,"Healthy",IF(C29/D29&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D29=0,"",IF(C29/D29&lt;=1.2,"Healthy",IF(C29/D29&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1651,7 +1645,7 @@
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>IF(D30=0,"",IF(C30/D30&lt;1.2,"Healthy",IF(C30/D30&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D30=0,"",IF(C30/D30&lt;=1.2,"Healthy",IF(C30/D30&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1665,7 +1659,7 @@
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>IF(D31=0,"",IF(C31/D31&lt;1.2,"Healthy",IF(C31/D31&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D31=0,"",IF(C31/D31&lt;=1.2,"Healthy",IF(C31/D31&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1679,7 +1673,7 @@
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>IF(D32=0,"",IF(C32/D32&lt;1.2,"Healthy",IF(C32/D32&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D32=0,"",IF(C32/D32&lt;=1.2,"Healthy",IF(C32/D32&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1687,7 @@
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>IF(D33=0,"",IF(C33/D33&lt;1.2,"Healthy",IF(C33/D33&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D33=0,"",IF(C33/D33&lt;=1.2,"Healthy",IF(C33/D33&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1707,7 +1701,7 @@
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>IF(D34=0,"",IF(C34/D34&lt;1.2,"Healthy",IF(C34/D34&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D34=0,"",IF(C34/D34&lt;=1.2,"Healthy",IF(C34/D34&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1721,7 +1715,7 @@
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>IF(D35=0,"",IF(C35/D35&lt;1.2,"Healthy",IF(C35/D35&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D35=0,"",IF(C35/D35&lt;=1.2,"Healthy",IF(C35/D35&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1729,7 @@
         <v/>
       </c>
       <c r="F36" s="9">
-        <f>IF(D36=0,"",IF(C36/D36&lt;1.2,"Healthy",IF(C36/D36&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D36=0,"",IF(C36/D36&lt;=1.2,"Healthy",IF(C36/D36&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1749,7 +1743,7 @@
         <v/>
       </c>
       <c r="F37" s="9">
-        <f>IF(D37=0,"",IF(C37/D37&lt;1.2,"Healthy",IF(C37/D37&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D37=0,"",IF(C37/D37&lt;=1.2,"Healthy",IF(C37/D37&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1763,7 +1757,7 @@
         <v/>
       </c>
       <c r="F38" s="9">
-        <f>IF(D38=0,"",IF(C38/D38&lt;1.2,"Healthy",IF(C38/D38&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D38=0,"",IF(C38/D38&lt;=1.2,"Healthy",IF(C38/D38&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1777,7 +1771,7 @@
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>IF(D39=0,"",IF(C39/D39&lt;1.2,"Healthy",IF(C39/D39&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D39=0,"",IF(C39/D39&lt;=1.2,"Healthy",IF(C39/D39&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1785,7 @@
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>IF(D40=0,"",IF(C40/D40&lt;1.2,"Healthy",IF(C40/D40&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D40=0,"",IF(C40/D40&lt;=1.2,"Healthy",IF(C40/D40&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1799,7 @@
         <v/>
       </c>
       <c r="F41" s="9">
-        <f>IF(D41=0,"",IF(C41/D41&lt;1.2,"Healthy",IF(C41/D41&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D41=0,"",IF(C41/D41&lt;=1.2,"Healthy",IF(C41/D41&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1819,7 +1813,7 @@
         <v/>
       </c>
       <c r="F42" s="9">
-        <f>IF(D42=0,"",IF(C42/D42&lt;1.2,"Healthy",IF(C42/D42&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D42=0,"",IF(C42/D42&lt;=1.2,"Healthy",IF(C42/D42&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1833,7 +1827,7 @@
         <v/>
       </c>
       <c r="F43" s="9">
-        <f>IF(D43=0,"",IF(C43/D43&lt;1.2,"Healthy",IF(C43/D43&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D43=0,"",IF(C43/D43&lt;=1.2,"Healthy",IF(C43/D43&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1847,7 +1841,7 @@
         <v/>
       </c>
       <c r="F44" s="9">
-        <f>IF(D44=0,"",IF(C44/D44&lt;1.2,"Healthy",IF(C44/D44&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D44=0,"",IF(C44/D44&lt;=1.2,"Healthy",IF(C44/D44&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1855,7 @@
         <v/>
       </c>
       <c r="F45" s="9">
-        <f>IF(D45=0,"",IF(C45/D45&lt;1.2,"Healthy",IF(C45/D45&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D45=0,"",IF(C45/D45&lt;=1.2,"Healthy",IF(C45/D45&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1875,7 +1869,7 @@
         <v/>
       </c>
       <c r="F46" s="9">
-        <f>IF(D46=0,"",IF(C46/D46&lt;1.2,"Healthy",IF(C46/D46&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D46=0,"",IF(C46/D46&lt;=1.2,"Healthy",IF(C46/D46&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1889,7 +1883,7 @@
         <v/>
       </c>
       <c r="F47" s="9">
-        <f>IF(D47=0,"",IF(C47/D47&lt;1.2,"Healthy",IF(C47/D47&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D47=0,"",IF(C47/D47&lt;=1.2,"Healthy",IF(C47/D47&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
@@ -1903,14 +1897,14 @@
         <v/>
       </c>
       <c r="F48" s="9">
-        <f>IF(D48=0,"",IF(C48/D48&lt;1.2,"Healthy",IF(C48/D48&lt;=2,"Watch — challenge at next change","ATTACK — prime target")))</f>
+        <f>IF(D48=0,"",IF(C48/D48&lt;=1.2,"Healthy",IF(C48/D48&lt;=2,"Watch: challenge at next change","Target")))</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Worth = the lowest cost that could still reliably perform the function (cheapest solution in any industry, physics floor, or historical best). VI &lt; 1.2 = healthy (green) · 1.2–2.0 = watch (amber) · &gt; 2.0 = attack (red). Type is a dropdown (Basic / Secondary).</t>
+          <t>Worth = the lowest cost that could still reliably perform the function (cheapest solution in any industry, physics floor, or historical best). VI up to 1.2 = healthy (green) · over 1.2 to 2.0 = watch (amber) · over 2.0 = target (red). Type is a dropdown (Basic / Secondary).</t>
         </is>
       </c>
     </row>
